--- a/jogos_2025-01-30.xlsx
+++ b/jogos_2025-01-30.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Al Bataeh</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Shabab Al Ahli Dubai</t>
+          <t>Al Ain</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>12.7</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>['39']</t>
+          <t>['9', '12']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['19', '45+2', '68']</t>
+          <t>['47', '58']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45687.42708333334</v>
@@ -772,109 +772,109 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Bataeh</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Ain</t>
+          <t>Shabab Al Ahli Dubai</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>['9', '12']</t>
+          <t>['39']</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>['47', '58']</t>
+          <t>['19', '45+2', '68']</t>
         </is>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45687.42708333334</v>
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,22 +901,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Qatar SC</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Al Shamal</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.07</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>2.02</v>
+        <v>6.25</v>
       </c>
       <c r="O4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T4" t="n">
         <v>3.5</v>
       </c>
-      <c r="P4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.25</v>
-      </c>
       <c r="U4" t="n">
-        <v>1.57</v>
+        <v>1.26</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AB4" t="n">
         <v>1.13</v>
       </c>
-      <c r="X4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AC4" t="n">
-        <v>1.5</v>
+        <v>2.71</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>['45+3', '90+10']</t>
+          <t>['74', '90+2']</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['82']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.73</v>
+        <v>1.19</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.34</v>
+        <v>1.72</v>
       </c>
       <c r="AI4" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.62</v>
+        <v>4.75</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45687.4375</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>Qatar SC</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Al Shamal</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.6</v>
+        <v>3.07</v>
       </c>
       <c r="M5" t="n">
-        <v>3.1</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>6.25</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.38</v>
       </c>
-      <c r="P5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="Q5" t="n">
-        <v>7.5</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U5" t="n">
         <v>1.57</v>
       </c>
-      <c r="S5" t="n">
+      <c r="V5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['45+3', '90+10']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['82']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI5" t="n">
         <v>2.25</v>
       </c>
-      <c r="T5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="X5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['74', '90+2']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.44</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>4.75</v>
+        <v>1.62</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45687.4375</v>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Katsina United</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="M8" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="N8" t="n">
-        <v>6.05</v>
+        <v>4.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="P8" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
         <v>8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="S8" t="n">
-        <v>2.02</v>
+        <v>2.17</v>
       </c>
       <c r="T8" t="n">
-        <v>4.75</v>
+        <v>4.15</v>
       </c>
       <c r="U8" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="X8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['90+6']</t>
+          <t>['1', '86']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AJ8" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45687.5</v>
@@ -1546,25 +1546,25 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Bendel Insurance</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1572,43 +1572,43 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="M9" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4.75</v>
+        <v>12</v>
       </c>
       <c r="O9" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P9" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="R9" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>2.53</v>
       </c>
       <c r="T9" t="n">
-        <v>4.15</v>
+        <v>3.42</v>
       </c>
       <c r="U9" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.73</v>
+        <v>1.37</v>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="Y9" t="n">
         <v>2.7</v>
@@ -1617,38 +1617,38 @@
         <v>1.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>5.8</v>
+        <v>4.45</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['1', '86']</t>
+          <t>['35', '52']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['90']</t>
+          <t>['6', '50']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.18</v>
+        <v>2.7</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.33</v>
+        <v>13</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45687.5</v>
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Katsina United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bendel Insurance</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.3</v>
+        <v>1.65</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>12</v>
+        <v>6.05</v>
       </c>
       <c r="O10" t="n">
-        <v>1.91</v>
+        <v>2.24</v>
       </c>
       <c r="P10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>8</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="X10" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q10" t="n">
-        <v>13</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="X10" t="n">
-        <v>2.66</v>
-      </c>
       <c r="Y10" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.45</v>
+        <v>7.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.95</v>
+        <v>2.98</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['35', '52']</t>
+          <t>['90+6']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['6', '50']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG10" t="n">
         <v>1.04</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.7</v>
+        <v>2.22</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.13</v>
+        <v>1.44</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13</v>
+        <v>4.15</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45687.5</v>
@@ -2697,119 +2697,119 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aldosivi</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N18" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC18" t="n">
         <v>2</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L18" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="O18" t="n">
+      <c r="AD18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI18" t="n">
         <v>4</v>
       </c>
-      <c r="P18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>['4', '25', '49', '68', '84']</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AJ18" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45687.70833333334</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Vere United</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="M19" t="n">
-        <v>4.33</v>
+        <v>8</v>
       </c>
       <c r="N19" t="n">
-        <v>1.42</v>
+        <v>19</v>
       </c>
       <c r="O19" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.95</v>
+        <v>15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.31</v>
+        <v>1.17</v>
       </c>
       <c r="S19" t="n">
-        <v>3.15</v>
+        <v>4.5</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>1.84</v>
       </c>
       <c r="U19" t="n">
-        <v>1.5</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.23</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>3.75</v>
+        <v>8</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.85</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.95</v>
+        <v>2.75</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.39</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '34', '70', '89']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['23']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>2.23</v>
+        <v>1.02</v>
       </c>
       <c r="AH19" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AI19" t="n">
         <v>1.1</v>
       </c>
-      <c r="AI19" t="n">
-        <v>4</v>
-      </c>
       <c r="AJ19" t="n">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45687.70833333334</v>
@@ -2955,119 +2955,119 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Aldosivi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vere United</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M20" t="n">
-        <v>8</v>
-      </c>
-      <c r="N20" t="n">
-        <v>19</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.4</v>
-      </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="Q20" t="n">
-        <v>15</v>
+        <v>3.25</v>
       </c>
       <c r="R20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.17</v>
       </c>
-      <c r="S20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X20" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC20" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['2', '34', '70', '89']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['23']</t>
+          <t>['4', '25', '49', '68', '84']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.02</v>
+        <v>1.49</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.8</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.1</v>
+        <v>2.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>1.91</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45687.70833333334</v>
@@ -3739,16 +3739,16 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Argentinos Juniors</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Atlético Tucumán</t>
+          <t>Tigre</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -3765,22 +3765,22 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="O26" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="P26" t="n">
         <v>1.91</v>
       </c>
       <c r="Q26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
         <v>1.62</v>
@@ -3798,32 +3798,32 @@
         <v>1.12</v>
       </c>
       <c r="W26" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="X26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AA26" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['44', '55']</t>
+          <t>['20']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
@@ -3832,16 +3832,16 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45687.89583333334</v>
@@ -3868,16 +3868,16 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Argentinos Juniors</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tigre</t>
+          <t>Atlético Tucumán</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3894,22 +3894,22 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="P27" t="n">
         <v>1.91</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
         <v>1.62</v>
@@ -3927,32 +3927,32 @@
         <v>1.12</v>
       </c>
       <c r="W27" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="X27" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AA27" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>['20']</t>
+          <t>['44', '55']</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
@@ -3961,16 +3961,16 @@
         </is>
       </c>
       <c r="AG27" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45687.89583333334</v>
